--- a/docs/downloads/10/tbl_menaces_alaotra_tous.xlsx
+++ b/docs/downloads/10/tbl_menaces_alaotra_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -399,7 +399,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -419,7 +419,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -439,7 +439,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -459,7 +459,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -499,7 +499,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -539,7 +539,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -559,7 +559,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -579,7 +579,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -599,7 +599,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -679,7 +679,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -699,7 +699,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -759,7 +759,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -779,7 +779,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -819,7 +819,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -839,7 +839,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -859,7 +859,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -879,7 +879,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -899,7 +899,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -919,7 +919,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -939,7 +939,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -979,7 +979,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -999,7 +999,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1039,7 +1039,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1059,7 +1059,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1079,7 +1079,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1099,7 +1099,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1119,7 +1119,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1139,7 +1139,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1159,7 +1159,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1179,7 +1179,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1199,7 +1199,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1219,7 +1219,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1239,7 +1239,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1259,7 +1259,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1279,7 +1279,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1299,7 +1299,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1319,7 +1319,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1339,7 +1339,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1359,7 +1359,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1379,7 +1379,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1399,7 +1399,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1439,7 +1439,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1459,7 +1459,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1479,7 +1479,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1499,7 +1499,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1519,7 +1519,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1539,7 +1539,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1559,7 +1559,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1579,7 +1579,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1619,7 +1619,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1639,7 +1639,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1679,7 +1679,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1699,7 +1699,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1719,7 +1719,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1739,7 +1739,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1779,7 +1779,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1799,7 +1799,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1819,7 +1819,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1839,7 +1839,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1859,7 +1859,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1879,7 +1879,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1899,7 +1899,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1919,7 +1919,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1939,7 +1939,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1959,7 +1959,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1979,7 +1979,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1999,7 +1999,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2039,7 +2039,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2059,7 +2059,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2079,7 +2079,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2099,7 +2099,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2119,7 +2119,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2159,7 +2159,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2179,7 +2179,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2199,7 +2199,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2219,7 +2219,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2239,7 +2239,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2259,7 +2259,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2299,7 +2299,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2319,7 +2319,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2339,7 +2339,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2359,7 +2359,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2379,7 +2379,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2399,7 +2399,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2419,7 +2419,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2439,7 +2439,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2459,7 +2459,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2479,7 +2479,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2499,7 +2499,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2519,7 +2519,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2539,7 +2539,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2559,7 +2559,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2579,7 +2579,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2599,7 +2599,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2619,7 +2619,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2639,7 +2639,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2659,7 +2659,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2679,7 +2679,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2699,7 +2699,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2719,7 +2719,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2739,7 +2739,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2759,7 +2759,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2779,7 +2779,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2799,7 +2799,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2819,7 +2819,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -2839,7 +2839,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -2859,7 +2859,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -2879,7 +2879,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -2899,7 +2899,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2919,7 +2919,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -2939,7 +2939,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -2959,7 +2959,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -2979,7 +2979,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -2999,7 +2999,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3019,7 +3019,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3039,7 +3039,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3059,7 +3059,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3079,7 +3079,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3099,7 +3099,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3119,7 +3119,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3139,7 +3139,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3159,7 +3159,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3179,7 +3179,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3199,7 +3199,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3219,7 +3219,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3239,7 +3239,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3259,7 +3259,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3279,7 +3279,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3299,7 +3299,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3319,7 +3319,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3339,7 +3339,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3359,7 +3359,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3379,7 +3379,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3399,7 +3399,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3419,7 +3419,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3439,7 +3439,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3459,7 +3459,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -3479,7 +3479,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -3499,7 +3499,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -3519,7 +3519,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -3539,7 +3539,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -3559,7 +3559,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -3579,7 +3579,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -3599,7 +3599,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
